--- a/离线语言_协议/词表协议.xlsx
+++ b/离线语言_协议/词表协议.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\soft\vscode\git\Ergo_Dock\离线语言_协议\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Ergo_Dock\离线语言_协议\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,178 +24,216 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+  <si>
+    <t>Hello Bed</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 02 00 22 FB</t>
+  </si>
+  <si>
+    <t>STOP</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 03 00 23 FB</t>
+  </si>
+  <si>
+    <t>All Up</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 04 00 24 FB</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 05 00 25 FB</t>
+  </si>
+  <si>
+    <t>Flat Preset</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 06 00 26 FB</t>
+  </si>
+  <si>
+    <t>Favorite preset</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 07 00 27 FB</t>
+  </si>
+  <si>
+    <t>Tv preset</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 08 00 28 FB</t>
+  </si>
+  <si>
+    <t>Raise-head</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 09 00 29 FB</t>
+  </si>
+  <si>
+    <t>Lower-head</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0A 00 2A FB</t>
+  </si>
+  <si>
+    <t>Raise-foot</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0B 00 2B FB</t>
+  </si>
+  <si>
+    <t>Lower foot</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0C 00 2C FB</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0D 00 2D FB</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0E 00 2E FB</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 0F 00 2F FB</t>
+  </si>
+  <si>
+    <t>MASSAGE OFF</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 10 00 30 FB</t>
+  </si>
+  <si>
+    <t>LIGHT OFF</t>
+  </si>
+  <si>
+    <t>A5 FA 00 81 11 00 31 FB</t>
+  </si>
+  <si>
+    <t>LIGHT ON</t>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发送协议</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GOOD NIGHT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 12 00 32 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 12 00 33 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zero G/ZERO-GRAVITY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ANTI-SNORE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 12 00 34 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAISE LUMBAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 12 00 35 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOWER LUMBAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAISE TILT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOWER TILT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 12 00 36 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 12 00 37 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Massage On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Massage UP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Massage Dwon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 12 00 38 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 01 00 21 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 02 00 22 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接收</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 01 00 21 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 82 01 00 22 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用唤醒词1唤醒，屏蔽唤醒词2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用唤醒词2唤醒，屏蔽唤醒词1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音芯片关闭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 01 00 20 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>Hello Ergo</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 01 00 21 FB</t>
-  </si>
-  <si>
-    <t>Hello Bed</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 02 00 22 FB</t>
-  </si>
-  <si>
-    <t>STOP</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 03 00 23 FB</t>
-  </si>
-  <si>
-    <t>All Up</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 04 00 24 FB</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 05 00 25 FB</t>
-  </si>
-  <si>
-    <t>Flat Preset</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 06 00 26 FB</t>
-  </si>
-  <si>
-    <t>Favorite preset</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 07 00 27 FB</t>
-  </si>
-  <si>
-    <t>Tv preset</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 08 00 28 FB</t>
-  </si>
-  <si>
-    <t>Raise-head</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 09 00 29 FB</t>
-  </si>
-  <si>
-    <t>Lower-head</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0A 00 2A FB</t>
-  </si>
-  <si>
-    <t>Raise-foot</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0B 00 2B FB</t>
-  </si>
-  <si>
-    <t>Lower foot</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0C 00 2C FB</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0D 00 2D FB</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0E 00 2E FB</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 0F 00 2F FB</t>
-  </si>
-  <si>
-    <t>MASSAGE OFF</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 10 00 30 FB</t>
-  </si>
-  <si>
-    <t>LIGHT OFF</t>
-  </si>
-  <si>
-    <t>A5 FA 00 81 11 00 31 FB</t>
-  </si>
-  <si>
-    <t>LIGHT ON</t>
-  </si>
-  <si>
-    <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>命令词</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发送协议</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GOOD NIGHT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 32 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 33 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zero G/ZERO-GRAVITY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ANTI-SNORE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 34 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RAISE LUMBAR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 35 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOWER LUMBAR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RAISE TILT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOWER TILT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 36 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 37 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Massage On</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Massage UP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Massage Dwon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 38 FB</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -203,7 +241,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,6 +280,19 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -251,7 +302,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -388,31 +439,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -693,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" bestFit="1" customWidth="1"/>
@@ -701,280 +764,334 @@
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
+      <c r="E1" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="E3" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="C4" s="12" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="B5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="C7" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C8" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C9" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C10" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C11" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C12" s="12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C13" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="13">
+        <v>13</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
-        <v>13</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>14</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>15</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C18" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>18</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
         <v>19</v>
       </c>
       <c r="B20" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="19" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="18">
+        <v>20</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
-        <v>20</v>
-      </c>
-      <c r="B21" s="19" t="s">
+      <c r="C21" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="18">
+        <v>21</v>
+      </c>
+      <c r="B22" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="19">
-        <v>21</v>
-      </c>
-      <c r="B22" s="19" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="18">
+        <v>22</v>
+      </c>
+      <c r="B23" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C23" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="18">
+        <v>23</v>
+      </c>
+      <c r="B24" s="18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="19">
-        <v>22</v>
-      </c>
-      <c r="B23" s="19" t="s">
+      <c r="C24" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
+        <v>24</v>
+      </c>
+      <c r="B25" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="19">
-        <v>23</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="19">
-        <v>24</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>50</v>
-      </c>
+      <c r="C25" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="B26" s="20"/>
+      <c r="C26" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/离线语言_协议/词表协议.xlsx
+++ b/离线语言_协议/词表协议.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Hello Bed</t>
   </si>
@@ -129,111 +129,115 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Zero G/ZERO-GRAVITY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ANTI-SNORE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAISE LUMBAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOWER LUMBAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAISE TILT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOWER TILT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Massage On</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Massage UP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Massage Dwon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 01 00 21 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 02 00 22 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接收</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 01 00 21 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 82 01 00 22 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用唤醒词1唤醒，屏蔽唤醒词2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用唤醒词2唤醒，屏蔽唤醒词1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音芯片关闭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 01 00 20 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hello Ergo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>A5 FA 00 81 12 00 32 FB</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A5 FA 00 81 12 00 33 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zero G/ZERO-GRAVITY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ANTI-SNORE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 34 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RAISE LUMBAR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 35 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOWER LUMBAR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RAISE TILT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOWER TILT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 36 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 37 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Massage On</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Massage UP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Massage Dwon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 12 00 38 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 01 00 21 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 02 00 22 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>接收</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 01 00 21 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 82 01 00 22 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用唤醒词1唤醒，屏蔽唤醒词2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用唤醒词2唤醒，屏蔽唤醒词1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语音芯片关闭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5 FA 00 81 01 00 20 FB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hello Ergo</t>
+    <t>A5 FA 00 81 13 00 33 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 14 00 34 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 15 00 35 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 16 00 36 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 17 00 37 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A5 FA 00 81 18 00 38 FB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令词（日语）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -302,7 +306,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -450,11 +454,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -476,6 +517,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -756,342 +804,379 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="G1" s="19" t="s">
+        <v>44</v>
+      </c>
       <c r="H1" s="20"/>
       <c r="I1" s="20"/>
       <c r="J1" s="20"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="G2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="22"/>
+      <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20" t="s">
-        <v>54</v>
-      </c>
+      <c r="G3" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="20"/>
       <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J3" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="23"/>
+      <c r="D4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20" t="s">
-        <v>55</v>
-      </c>
+      <c r="G4" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="20"/>
       <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J4" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="23"/>
+      <c r="D7" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="23"/>
+      <c r="D8" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="23"/>
+      <c r="D9" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="23"/>
+      <c r="D10" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="23"/>
+      <c r="D11" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="23"/>
+      <c r="D12" s="12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="23"/>
+      <c r="D13" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>13</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="24"/>
+      <c r="D14" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>14</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="24"/>
+      <c r="D15" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>15</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="24"/>
+      <c r="D16" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="23"/>
+      <c r="D17" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="23"/>
+      <c r="D18" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>18</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="25"/>
+      <c r="D19" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
         <v>19</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="18"/>
+      <c r="D20" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="18">
         <v>20</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
         <v>21</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
         <v>22</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="18">
         <v>23</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
         <v>24</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+        <v>38</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
         <v>25</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="8"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" s="20"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D28" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
